--- a/contact_forms/020_store_locator_search_form--contact_forms.xlsx
+++ b/contact_forms/020_store_locator_search_form--contact_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -762,8 +762,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -791,12 +791,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'store',_'text':_'store'}</t>
+          <t>store</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'store', 'text': 'Store'}</t>
+          <t>store</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'mall',_'text':_'mall'}</t>
+          <t>mall</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'mall', 'text': 'Mall'}</t>
+          <t>mall</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'strip',_'text':_'strip'}</t>
+          <t>strip</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'strip', 'text': 'Strip'}</t>
+          <t>strip</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'market',_'text':_'market'}</t>
+          <t>market</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'market', 'text': 'Market'}</t>
+          <t>market</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'nearby',_'text':_'nearby'}</t>
+          <t>nearby</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'nearby', 'text': 'Nearby'}</t>
+          <t>nearby</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'within_walking_distance',_'text':_'within_walking_distance'}</t>
+          <t>within_walking_distance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'within_walking_distance', 'text': 'Within walking distance'}</t>
+          <t>within walking distance</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'within_driving_distance',_'text':_'within_driving_distance'}</t>
+          <t>within_driving_distance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'within_driving_distance', 'text': 'Within driving distance'}</t>
+          <t>within driving distance</t>
         </is>
       </c>
     </row>
